--- a/plantilla/FGR-29_v3_plantilla.xlsx
+++ b/plantilla/FGR-29_v3_plantilla.xlsx
@@ -3592,11 +3592,7 @@
         </is>
       </c>
       <c r="B62" s="130" t="n"/>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>Nicolás Villegas Echavarría</t>
-        </is>
-      </c>
+      <c r="C62" s="18" t="n"/>
       <c r="D62" s="130" t="n"/>
       <c r="E62" s="6" t="n"/>
       <c r="F62" s="130" t="n"/>
@@ -3608,11 +3604,7 @@
         </is>
       </c>
       <c r="B63" s="130" t="n"/>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>1.037.625.350</t>
-        </is>
-      </c>
+      <c r="C63" s="18" t="n"/>
       <c r="D63" s="130" t="n"/>
       <c r="E63" s="164" t="n"/>
       <c r="F63" s="130" t="n"/>
@@ -3624,11 +3616,7 @@
         </is>
       </c>
       <c r="B64" s="130" t="n"/>
-      <c r="C64" s="18" t="inlineStr">
-        <is>
-          <t>Cl 46 # 70 A 65 Laureles - Estadio, Medellín</t>
-        </is>
-      </c>
+      <c r="C64" s="18" t="n"/>
       <c r="D64" s="130" t="n"/>
       <c r="E64" s="164" t="n"/>
       <c r="F64" s="130" t="n"/>
@@ -3640,9 +3628,7 @@
         </is>
       </c>
       <c r="B65" s="130" t="n"/>
-      <c r="C65" s="18" t="n">
-        <v>3226194274</v>
-      </c>
+      <c r="C65" s="18" t="n"/>
       <c r="D65" s="130" t="n"/>
       <c r="E65" s="164" t="n"/>
       <c r="F65" s="130" t="n"/>
@@ -3685,9 +3671,9 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C62:D62"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A50:F50"/>

--- a/plantilla/FGR-29_v3_plantilla.xlsx
+++ b/plantilla/FGR-29_v3_plantilla.xlsx
@@ -950,47 +950,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>723900</colOff>
-      <row>65</row>
-      <rowOff>124883</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>970915</colOff>
-      <row>65</row>
-      <rowOff>517313</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 10" descr="Texto  Descripción generada automáticamente"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4440767" y="13248216"/>
-          <a:ext cx="1877483" cy="400050"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -3671,9 +3630,9 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A50:F50"/>
